--- a/assessment/risk_tables/sc12-jm10_2024.xlsx
+++ b/assessment/risk_tables/sc12-jm10_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leeqi/Library/CloudStorage/GoogleDrive-leeqi@uw.edu/My Drive/SPRFMO/jjm/assessment/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leeqi/Library/CloudStorage/GoogleDrive-leeqi@uw.edu/My Drive/SPRFMO/jjm/assessment/risk_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{930BE6DF-A360-F042-B0E4-8D0177C5255D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B1A17A-6C81-7D44-9C32-57AE180D1A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{1354E36E-017E-074A-9785-0738E9F904BC}"/>
+    <workbookView xWindow="38400" yWindow="-8320" windowWidth="14400" windowHeight="25340" xr2:uid="{1354E36E-017E-074A-9785-0738E9F904BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -637,58 +637,58 @@
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1">
-        <v>17331</v>
-      </c>
-      <c r="C6" s="1">
-        <v>100</v>
-      </c>
-      <c r="D6" s="1">
-        <v>13489</v>
-      </c>
-      <c r="E6" s="1">
-        <v>94</v>
-      </c>
-      <c r="F6" s="1">
-        <v>11660</v>
-      </c>
-      <c r="G6" s="1">
-        <v>80</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1117</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1337</v>
+      <c r="B6">
+        <v>15633</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>10810</v>
+      </c>
+      <c r="E6">
+        <v>76</v>
+      </c>
+      <c r="F6">
+        <v>9309</v>
+      </c>
+      <c r="G6">
+        <v>55</v>
+      </c>
+      <c r="H6">
+        <v>2115</v>
+      </c>
+      <c r="I6">
+        <v>2248</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="1">
-        <v>16159</v>
-      </c>
-      <c r="C7" s="1">
-        <v>100</v>
-      </c>
-      <c r="D7" s="1">
-        <v>11534</v>
-      </c>
-      <c r="E7" s="1">
-        <v>83</v>
-      </c>
-      <c r="F7" s="1">
-        <v>9933</v>
-      </c>
-      <c r="G7" s="1">
-        <v>63</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1794</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1981</v>
+      <c r="B7">
+        <v>14682</v>
+      </c>
+      <c r="C7">
+        <v>99</v>
+      </c>
+      <c r="D7">
+        <v>9672</v>
+      </c>
+      <c r="E7">
+        <v>62</v>
+      </c>
+      <c r="F7">
+        <v>8329</v>
+      </c>
+      <c r="G7">
+        <v>41</v>
+      </c>
+      <c r="H7">
+        <v>2724</v>
+      </c>
+      <c r="I7">
+        <v>2696</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.2">

--- a/assessment/risk_tables/sc12-jm10_2024.xlsx
+++ b/assessment/risk_tables/sc12-jm10_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leeqi/Library/CloudStorage/GoogleDrive-leeqi@uw.edu/My Drive/SPRFMO/jjm/assessment/risk_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B1A17A-6C81-7D44-9C32-57AE180D1A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7DD08B-9628-DE4F-90E2-1EDC18688170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="-8320" windowWidth="14400" windowHeight="25340" xr2:uid="{1354E36E-017E-074A-9785-0738E9F904BC}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="9440" xr2:uid="{1354E36E-017E-074A-9785-0738E9F904BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -136,11 +136,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -489,7 +486,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B1" t="s">
@@ -518,123 +515,123 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>19461</v>
       </c>
-      <c r="C2" s="2">
-        <v>100</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="C2" s="1">
+        <v>100</v>
+      </c>
+      <c r="D2" s="1">
         <v>19008</v>
       </c>
-      <c r="E2" s="2">
-        <v>100</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="E2" s="1">
+        <v>100</v>
+      </c>
+      <c r="F2" s="1">
         <v>17509</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>99</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>0</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>17331</v>
       </c>
-      <c r="C3" s="2">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="C3" s="1">
+        <v>100</v>
+      </c>
+      <c r="D3" s="1">
         <v>13489</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>94</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>11660</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>80</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>1117</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <v>1337</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>16724</v>
       </c>
-      <c r="C4" s="2">
-        <v>100</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="C4" s="1">
+        <v>100</v>
+      </c>
+      <c r="D4" s="1">
         <v>12409</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>90</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>10694</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>72</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>1462</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="1">
         <v>1679</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>16159</v>
       </c>
-      <c r="C5" s="2">
-        <v>100</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="C5" s="1">
+        <v>100</v>
+      </c>
+      <c r="D5" s="1">
         <v>11534</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>83</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>9933</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>63</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>1794</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="1">
         <v>1981</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6">
@@ -663,7 +660,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B7">
@@ -692,176 +689,176 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>11598</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>93</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>6852</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>14</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>5847</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <v>6</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>4997</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="1">
         <v>3818</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>17108</v>
       </c>
-      <c r="C9" s="3">
-        <v>100</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
         <v>13073</v>
       </c>
-      <c r="E9" s="3">
-        <v>100</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="E9">
+        <v>93</v>
+      </c>
+      <c r="F9">
         <v>11284</v>
       </c>
-      <c r="G9" s="3">
-        <v>96</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="G9">
+        <v>77</v>
+      </c>
+      <c r="H9">
         <v>1242</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9">
         <v>1464</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>16781</v>
       </c>
-      <c r="C10" s="3">
-        <v>100</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10">
         <v>12504</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10">
+        <v>90</v>
+      </c>
+      <c r="F10">
+        <v>10779</v>
+      </c>
+      <c r="G10">
+        <v>72</v>
+      </c>
+      <c r="H10">
+        <v>1428</v>
+      </c>
+      <c r="I10">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>16674</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>12327</v>
+      </c>
+      <c r="E11">
+        <v>89</v>
+      </c>
+      <c r="F11">
+        <v>10622</v>
+      </c>
+      <c r="G11">
+        <v>71</v>
+      </c>
+      <c r="H11">
+        <v>1490</v>
+      </c>
+      <c r="I11">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>15539</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
+        <v>10688</v>
+      </c>
+      <c r="E12">
+        <v>75</v>
+      </c>
+      <c r="F12">
+        <v>9204</v>
+      </c>
+      <c r="G12">
+        <v>54</v>
+      </c>
+      <c r="H12">
+        <v>2174</v>
+      </c>
+      <c r="I12">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>15049</v>
+      </c>
+      <c r="C13">
         <v>99</v>
       </c>
-      <c r="F10" s="3">
-        <v>10779</v>
-      </c>
-      <c r="G10" s="3">
-        <v>95</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1428</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1647</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3">
-        <v>16674</v>
-      </c>
-      <c r="C11" s="3">
-        <v>100</v>
-      </c>
-      <c r="D11" s="3">
-        <v>12327</v>
-      </c>
-      <c r="E11" s="3">
-        <v>99</v>
-      </c>
-      <c r="F11" s="3">
-        <v>10622</v>
-      </c>
-      <c r="G11" s="3">
-        <v>95</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1490</v>
-      </c>
-      <c r="I11" s="3">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1">
-        <v>15539</v>
-      </c>
-      <c r="C12" s="1">
-        <v>100</v>
-      </c>
-      <c r="D12" s="1">
-        <v>10688</v>
-      </c>
-      <c r="E12" s="1">
-        <v>75</v>
-      </c>
-      <c r="F12" s="1">
-        <v>9204</v>
-      </c>
-      <c r="G12" s="1">
-        <v>54</v>
-      </c>
-      <c r="H12" s="1">
-        <v>2174</v>
-      </c>
-      <c r="I12" s="1">
-        <v>2295</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1">
-        <v>15049</v>
-      </c>
-      <c r="C13" s="1">
-        <v>99</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="D13">
         <v>10089</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13">
         <v>67</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13">
         <v>8688</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13">
         <v>46</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13">
         <v>2484</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13">
         <v>2529</v>
       </c>
     </row>
